--- a/UPACI_Project_Deviation_Report.xlsx
+++ b/UPACI_Project_Deviation_Report.xlsx
@@ -408,6 +408,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I9"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+    <col min="9" max="9" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -571,7 +582,7 @@
         <v>NOT INSTALLED</v>
       </c>
       <c r="F6" t="str">
-        <v>US_003/task_004</v>
+        <v>US_003/task_004, US_007/task_001, US_008/task_001</v>
       </c>
       <c r="G6" t="str">
         <v>MEDIUM</v>
@@ -671,8 +682,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I9"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
@@ -681,7 +690,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G23"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="53.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1051,16 +1069,187 @@
         <v>AuthSession, JwtPayload, AuthRequest, TokenBlacklist all in auth.types.ts. No separate session types file.</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>US_007/task_001 (DB Core Schema)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>database/migrations/001_create_users_table.js</v>
+      </c>
+      <c r="D17" t="str">
+        <v>database/migrations/V001__create_core_tables.sql</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Architecture Change</v>
+      </c>
+      <c r="F17" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Task spec expects 11 node-pg-migrate JS files (001-011). Actual: 39 raw SQL files (V001-V039) using Flyway-style naming. All 9 required tables exist across V001-V004.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>US_007/task_001 (DB Core Schema)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>database/schema/ERD.md</v>
+      </c>
+      <c r="D18" t="str">
+        <v>database/schema/ERD_diagram.md</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Renamed</v>
+      </c>
+      <c r="F18" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="G18" t="str">
+        <v>ERD documentation exists but with different filename. Content matches expected requirements.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>US_007/task_001 (DB Core Schema)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>database/schema/DATA_DICTIONARY.md</v>
+      </c>
+      <c r="D19" t="str">
+        <v>database/schema/TABLE_DEFINITIONS.md</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Renamed</v>
+      </c>
+      <c r="F19" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Data dictionary exists as TABLE_DEFINITIONS.md. Covers all table/column documentation.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>US_007/task_001 (DB Core Schema)</v>
+      </c>
+      <c r="C20" t="str">
+        <v>database/seeds/001_initial_data.js</v>
+      </c>
+      <c r="D20" t="str">
+        <v>database/seeds/ (multiple SQL seed files)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Architecture Change</v>
+      </c>
+      <c r="F20" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Seed data uses raw SQL files in seeds/ directory instead of single JS file. Seed data is present and functional.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>US_008/task_001 (DB Perf Indexes)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>database/migrations/012_create_performance_indexes.js</v>
+      </c>
+      <c r="D21" t="str">
+        <v>database/migrations/V005__create_indexes.sql + V039__performance_indexes.sql</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Architecture Change</v>
+      </c>
+      <c r="F21" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Task spec expects 4 JS migration files (012-015). Actual: indexes spread across V005, V006, V039 SQL files. All required indexes present (144 total).</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>US_005/task_001 (Prometheus Metrics)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>server/docs/METRICS_REFERENCE.md</v>
+      </c>
+      <c r="D22" t="str">
+        <v>server/docs/METRICS_REFERENCE.md</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Exists</v>
+      </c>
+      <c r="F22" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="G22" t="str">
+        <v>File exists at expected path. No deviation.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>US_006/task_001 (Grafana Dashboard)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>monitoring/prometheus/alerts.yml</v>
+      </c>
+      <c r="D23" t="str">
+        <v>monitoring/prometheus/alerts.yml</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Exists</v>
+      </c>
+      <c r="F23" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Alert rules file exists at expected path.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H15"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="56.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="58.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1296,18 +1485,181 @@
         <v>US_003 says 20, US_040 says 50. Code defaults to 50 but .env overrides to 20. Contradicting specs between tasks.</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>US_005/task_001 (Prometheus)</v>
+      </c>
+      <c r="C10" t="str">
+        <v>METRICS_AUTH_ENABLED default</v>
+      </c>
+      <c r="D10" t="str">
+        <v>true (task spec)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>false (was in .env, fixed to true)</v>
+      </c>
+      <c r="F10" t="str">
+        <v>server/.env</v>
+      </c>
+      <c r="G10" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Task spec and build commands say METRICS_AUTH_ENABLED=true. .env had it as false. Fixed during this audit session.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>US_005/task_001 (Prometheus)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>METRICS_AUTH_PASS</v>
+      </c>
+      <c r="D11" t="str">
+        <v>secure_password (task spec)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>admin (actual .env)</v>
+      </c>
+      <c r="F11" t="str">
+        <v>server/.env</v>
+      </c>
+      <c r="G11" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Task build commands use secure_password. Actual deployment uses admin. Prometheus config was also mismatched — fixed during audit to align both to admin.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>US_006/task_001 (Grafana)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Grafana alerting mode</v>
+      </c>
+      <c r="D12" t="str">
+        <v>[alerting] enabled = true (legacy)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>[alerting] enabled = false + [unified_alerting] enabled = true</v>
+      </c>
+      <c r="F12" t="str">
+        <v>monitoring/grafana/grafana.ini</v>
+      </c>
+      <c r="G12" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Both legacy and unified alerting were enabled causing Grafana crash loop. Fixed: disabled legacy alerting, kept unified alerting only.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>US_006/task_001 (Grafana)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Datasource provisioning YAML</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Valid YAML (manageAlerts: true)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Broken YAML (manageAlerts split across lines)</v>
+      </c>
+      <c r="F13" t="str">
+        <v>monitoring/grafana/provisioning/datasources/prometheus.yml</v>
+      </c>
+      <c r="G13" t="str">
+        <v>HIGH</v>
+      </c>
+      <c r="H13" t="str">
+        <v>YAML syntax error in datasource provisioning caused Grafana to fail loading Prometheus datasource. Fixed during audit.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>US_006/task_001 (Grafana)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Dashboard template variables</v>
+      </c>
+      <c r="D14" t="str">
+        <v>$environment, $service variables (per task spec)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Variables were missing from all 3 dashboards</v>
+      </c>
+      <c r="F14" t="str">
+        <v>monitoring/grafana/dashboards/*.json</v>
+      </c>
+      <c r="G14" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Task checklist requires $environment and $service template variables. Were absent from all dashboards. Added during this audit session.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>US_006/task_001 (Grafana)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>No-data panel behavior</v>
+      </c>
+      <c r="D15" t="str">
+        <v>"No data" with last query timestamp</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Panels had no noValue configured</v>
+      </c>
+      <c r="F15" t="str">
+        <v>monitoring/grafana/dashboards/upaci-system-health.json</v>
+      </c>
+      <c r="G15" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Task requires panels to show "No data" when Prometheus is unavailable. Stat/gauge panels had no noValue text. Added "No data - Prometheus unavailable" during audit.</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H9"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="44.83203125" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1562,18 +1914,93 @@
         <v>Test script is: "echo Error: no test specified &amp;&amp; exit 1". No test framework configured for backend.</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>EP-DATA</v>
+      </c>
+      <c r="C12" t="str">
+        <v>US_007/task_001 (DB Core Schema)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>database/tests/schema_validation.test.js</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="F12" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Task spec requires integration tests for table existence and constraint enforcement. No database/tests/ directory exists. Schema validated manually via SQL queries.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>EP-DATA</v>
+      </c>
+      <c r="C13" t="str">
+        <v>US_008/task_001 (DB Perf Indexes)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>database/tests/performance_benchmark.test.js</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="F13" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Task spec requires automated performance benchmark tests. No test file exists. Benchmarks verified manually (slot: 0.078ms, patient: 0.053ms, appt: 0.045ms — all pass).</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>EP-DATA</v>
+      </c>
+      <c r="C14" t="str">
+        <v>US_007/task_001 (DB Core Schema)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>schema_migrations tracking table</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Feature</v>
+      </c>
+      <c r="F14" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Task spec mentions schema_migrations table for tracking migration status. Not present — relies on idempotent IF NOT EXISTS DDL. Same as existing item #2 for US_003.</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F19"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1815,16 +2242,161 @@
         <v>Update task_003 Expected Changes table to reflect actual file paths used in the codebase.</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Stale Architecture</v>
+      </c>
+      <c r="C13" t="str">
+        <v>US_007/task_001 describes node-pg-migrate JS-based migration files (001_create_users_table.js). Actual project uses raw SQL files with Flyway-style naming (V001__create_core_tables.sql). 39 files vs expected 11.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>EP-DATA/us_007/task_001</v>
+      </c>
+      <c r="E13" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Rewrite Expected Changes table to reflect actual SQL migration structure with V-prefixed filenames.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Stale Architecture</v>
+      </c>
+      <c r="C14" t="str">
+        <v>US_008/task_001 describes node-pg-migrate JS-based index files (012-015_*.js). Actual indexes are in V005, V006, V039 SQL files. Migration numbering scheme completely different.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>EP-DATA/us_008/task_001</v>
+      </c>
+      <c r="E14" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Rewrite Expected Changes to list actual SQL files: V005__create_indexes.sql, V006__create_vector_indexes.sql, V039__performance_indexes.sql.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Stale File References</v>
+      </c>
+      <c r="C15" t="str">
+        <v>US_007/task_001 references database/schema/ERD.md and DATA_DICTIONARY.md. Actual filenames: ERD_diagram.md and TABLE_DEFINITIONS.md.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>EP-DATA/us_007/task_001</v>
+      </c>
+      <c r="E15" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Update task doc to reference actual filenames.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Column Naming Deviation</v>
+      </c>
+      <c r="C16" t="str">
+        <v>US_007/task_001 uses column name "active" for users table. Actual column is "is_active". Task says first_name is optional, actual is NOT NULL.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>EP-DATA/us_007/task_001</v>
+      </c>
+      <c r="E16" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Update Implementation Plan to match actual column names and constraints.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Outdated Stack Versions</v>
+      </c>
+      <c r="C17" t="str">
+        <v>US_005/task_001 specifies Express 4.x in Technology Stack table. Actual backend uses Express 5.2.1. US_006 specifies Grafana 10.x+ and Prometheus 2.x+ which match.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>EP-TECH/us_005/task_001</v>
+      </c>
+      <c r="E17" t="str">
+        <v>HIGH</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Update US_005 Technology Stack table to Express 5.x.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Scope Expansion</v>
+      </c>
+      <c r="C18" t="str">
+        <v>US_007 expected 9 tables and 11 migration files. Actual implementation has 29 tables and 39 migrations, far exceeding scope. Additional: medications, allergies, conversations, calendar_tokens, insurance_verifications, etc.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>EP-DATA/us_007/task_001</v>
+      </c>
+      <c r="E18" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Not a problem — implementation exceeds requirements. Document additional tables in DATA_DICTIONARY.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Performance Metrics Exceed Targets</v>
+      </c>
+      <c r="C19" t="str">
+        <v>US_008 targets: slot availability &lt;100ms, patient lookup &lt;200ms, appointment listing &lt;150ms. Actuals: 0.078ms, 0.053ms, 0.045ms. 144 indexes vs "20+" mentioned in docs.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>EP-DATA/us_008/task_001</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NONE</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Not a problem — performance far exceeds targets. Update docs with actual benchmark numbers.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C41"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1852,11 +2424,11 @@
       <c r="A3" t="str">
         <v>Tasks Audited This Session</v>
       </c>
-      <c r="B3" t="str">
-        <v>10</v>
+      <c r="B3">
+        <v>14</v>
       </c>
       <c r="C3" t="str">
-        <v>US_001/task_001, US_002/task_001, US_003/task_001-004, US_001/unittest, US_004/task_001-003</v>
+        <v>US_001/task_001, US_002/task_001, US_003/task_001-004, US_001/unittest, US_004/task_001-003, US_005/task_001, US_006/task_001, US_007/task_001, US_008/task_001</v>
       </c>
     </row>
     <row r="4">
@@ -2145,9 +2717,141 @@
         <v>Missing cross-refs, inconsistent naming, phantom deps, stale project state, duplicates</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>── SESSION 2 AUDIT (US_005-008) ──</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Tasks Audited (Session 2)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>4</v>
+      </c>
+      <c r="C32" t="str">
+        <v>US_005/task_001, US_006/task_001, US_007/task_001, US_008/task_001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>New Structure Deviations Added</v>
+      </c>
+      <c r="B33" t="str">
+        <v>7</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Migration file format (JS→SQL), schema doc renames</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>New Config Deviations Added</v>
+      </c>
+      <c r="B34" t="str">
+        <v>6</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Metrics auth, Grafana alerting, YAML errors, template variables, no-data handling</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>New Missing Items Added</v>
+      </c>
+      <c r="B35" t="str">
+        <v>3</v>
+      </c>
+      <c r="C35" t="str">
+        <v>schema_validation.test.js, performance_benchmark.test.js, schema_migrations table</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>New Doc Issues Added</v>
+      </c>
+      <c r="B36" t="str">
+        <v>7</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Stale architecture (node-pg-migrate→SQL), column naming, version mismatches, scope expansion</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Config Issues Fixed During Audit</v>
+      </c>
+      <c r="B37" t="str">
+        <v>6</v>
+      </c>
+      <c r="C37" t="str">
+        <v>METRICS_AUTH_ENABLED, Prometheus password, Grafana alerting conflict, YAML error, template variables, noValue panels</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>US_005 Verdict</v>
+      </c>
+      <c r="B38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="C38" t="str">
+        <v>All files exist. Config deviations fixed. Express version mismatch in docs.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>US_006 Verdict</v>
+      </c>
+      <c r="B39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="C39" t="str">
+        <v>All files exist. Template variables and no-data handling added. Grafana config issues fixed.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>US_007 Verdict</v>
+      </c>
+      <c r="B40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="C40" t="str">
+        <v>All 9 tables exist (29 total). Migration format differs (SQL vs JS). Schema docs renamed. No test file.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>US_008 Verdict</v>
+      </c>
+      <c r="B41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="C41" t="str">
+        <v>144 indexes (exceeds 20+ target). All benchmarks pass (&lt;100ms). Migration format differs. No test file.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C41"/>
   </ignoredErrors>
 </worksheet>
 </file>